--- a/data/trans_orig/P16A_n_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R2-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63199</t>
+          <t>64594</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>96401</t>
+          <t>97754</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56017</t>
+          <t>54253</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83925</t>
+          <t>85608</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>125989</t>
+          <t>127602</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>171552</t>
+          <t>170517</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>377375</t>
+          <t>376022</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>410577</t>
+          <t>409182</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>222755</t>
+          <t>221072</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>250663</t>
+          <t>252427</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>608905</t>
+          <t>609940</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>654468</t>
+          <t>652855</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,65%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39714</t>
+          <t>39366</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66094</t>
+          <t>67027</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70461</t>
+          <t>70835</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>104091</t>
+          <t>103732</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>117037</t>
+          <t>116855</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>159661</t>
+          <t>159758</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>300840</t>
+          <t>299907</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>327220</t>
+          <t>327568</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>267774</t>
+          <t>268133</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>301404</t>
+          <t>301030</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>579138</t>
+          <t>579041</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>621762</t>
+          <t>621944</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,18%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76095</t>
+          <t>77033</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>111896</t>
+          <t>111417</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35297</t>
+          <t>35128</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58292</t>
+          <t>58086</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117499</t>
+          <t>119456</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>158441</t>
+          <t>162950</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,95%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>430493</t>
+          <t>430972</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>466294</t>
+          <t>465356</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>109490</t>
+          <t>109696</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>132485</t>
+          <t>132654</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>551730</t>
+          <t>547221</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>592672</t>
+          <t>590715</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,18%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>239745</t>
+          <t>241643</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>299572</t>
+          <t>301820</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>164713</t>
+          <t>162956</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>209142</t>
+          <t>210140</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>418494</t>
+          <t>417959</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>492779</t>
+          <t>491417</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>938762</t>
+          <t>936514</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>998589</t>
+          <t>996691</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>505143</t>
+          <t>504145</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>549572</t>
+          <t>551329</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1459841</t>
+          <t>1461203</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1534126</t>
+          <t>1534661</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,59%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48276</t>
+          <t>48777</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>76669</t>
+          <t>76099</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>142799</t>
+          <t>141897</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>186298</t>
+          <t>187055</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>200326</t>
+          <t>199991</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>252665</t>
+          <t>254203</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,65%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>273886</t>
+          <t>274456</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>302279</t>
+          <t>301778</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>382454</t>
+          <t>381697</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>425953</t>
+          <t>426855</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>666642</t>
+          <t>665104</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>718981</t>
+          <t>719316</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,25%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26314</t>
+          <t>26010</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>421013</t>
+          <t>418682</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>489548</t>
+          <t>486354</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>436256</t>
+          <t>435135</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>507520</t>
+          <t>509440</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,93%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>271887</t>
+          <t>272191</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287881</t>
+          <t>287986</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>759212</t>
+          <t>762406</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>827747</t>
+          <t>830078</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1039440</t>
+          <t>1037520</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1110704</t>
+          <t>1111825</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,87%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>529650</t>
+          <t>531241</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>610366</t>
+          <t>616328</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>954313</t>
+          <t>956852</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1062304</t>
+          <t>1060443</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1515455</t>
+          <t>1499621</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1649740</t>
+          <t>1641852</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2659824</t>
+          <t>2653862</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2740540</t>
+          <t>2738949</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2315820</t>
+          <t>2317681</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2423811</t>
+          <t>2421272</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4998574</t>
+          <t>5006462</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5132859</t>
+          <t>5148693</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,44%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73970</t>
+          <t>74550</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>111423</t>
+          <t>112871</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61885</t>
+          <t>61600</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>95693</t>
+          <t>95650</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>145452</t>
+          <t>146848</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>196180</t>
+          <t>193388</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>325788</t>
+          <t>324340</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>363241</t>
+          <t>362661</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>218761</t>
+          <t>218804</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>252569</t>
+          <t>252854</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>555485</t>
+          <t>558277</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>606213</t>
+          <t>604817</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,46%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72151</t>
+          <t>71110</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>107767</t>
+          <t>106007</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77592</t>
+          <t>78309</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>113646</t>
+          <t>113982</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>162622</t>
+          <t>159357</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>212976</t>
+          <t>209058</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,62%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>311030</t>
+          <t>312790</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>346646</t>
+          <t>347687</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>224365</t>
+          <t>224029</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>260419</t>
+          <t>259702</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>543832</t>
+          <t>547750</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>594186</t>
+          <t>597451</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,94%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>168420</t>
+          <t>170545</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>215749</t>
+          <t>218878</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80991</t>
+          <t>83115</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>113180</t>
+          <t>114046</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>263677</t>
+          <t>261280</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>322341</t>
+          <t>320675</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,05%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>413666</t>
+          <t>410537</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>460995</t>
+          <t>458870</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>146949</t>
+          <t>146083</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>179138</t>
+          <t>177014</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>567203</t>
+          <t>568869</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>625867</t>
+          <t>628264</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,63%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>306781</t>
+          <t>303482</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>369726</t>
+          <t>368051</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>229508</t>
+          <t>227621</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>284589</t>
+          <t>282765</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>550721</t>
+          <t>550572</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>634977</t>
+          <t>637495</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>789283</t>
+          <t>790958</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>852228</t>
+          <t>855527</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>482068</t>
+          <t>483892</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>537149</t>
+          <t>539036</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1290690</t>
+          <t>1288172</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1374946</t>
+          <t>1375095</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,41%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>113415</t>
+          <t>114716</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>152299</t>
+          <t>153916</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>326893</t>
+          <t>330090</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>384955</t>
+          <t>385372</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>449819</t>
+          <t>452171</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>522622</t>
+          <t>523690</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,17%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>358297</t>
+          <t>356680</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>397181</t>
+          <t>395880</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>376567</t>
+          <t>376150</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>434629</t>
+          <t>431432</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>749496</t>
+          <t>748428</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>822299</t>
+          <t>819947</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,46%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13548</t>
+          <t>13179</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32641</t>
+          <t>32761</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>503510</t>
+          <t>504572</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>570276</t>
+          <t>569457</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>519054</t>
+          <t>519858</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>593548</t>
+          <t>596259</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,33%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>234241</t>
+          <t>234121</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>253334</t>
+          <t>253703</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>539075</t>
+          <t>539894</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>605841</t>
+          <t>604779</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>782685</t>
+          <t>779974</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>857179</t>
+          <t>856375</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,23%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>809013</t>
+          <t>815915</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>919920</t>
+          <t>922354</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1352936</t>
+          <t>1361852</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1478671</t>
+          <t>1481394</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2195565</t>
+          <t>2204525</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2363707</t>
+          <t>2361372</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,87%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2501990</t>
+          <t>2499556</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2612897</t>
+          <t>2605995</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2071454</t>
+          <t>2068731</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2197189</t>
+          <t>2188273</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4608328</t>
+          <t>4610663</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4776470</t>
+          <t>4767510</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,38%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76527</t>
+          <t>77313</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>113592</t>
+          <t>114515</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61580</t>
+          <t>61664</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>93133</t>
+          <t>93075</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>146273</t>
+          <t>146917</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>194277</t>
+          <t>195397</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,18%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>315500</t>
+          <t>314577</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>352565</t>
+          <t>351779</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>253922</t>
+          <t>253980</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285475</t>
+          <t>285391</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>581870</t>
+          <t>580750</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>629874</t>
+          <t>629230</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,07%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70987</t>
+          <t>67929</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>104003</t>
+          <t>101952</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74159</t>
+          <t>74904</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>109779</t>
+          <t>108301</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>150574</t>
+          <t>153795</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>200760</t>
+          <t>200305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,73%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>273224</t>
+          <t>275275</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>306240</t>
+          <t>309298</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>262494</t>
+          <t>263972</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>298114</t>
+          <t>297369</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>548740</t>
+          <t>549195</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>598926</t>
+          <t>595705</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,48%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>114928</t>
+          <t>116720</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>154568</t>
+          <t>155041</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52363</t>
+          <t>52733</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77643</t>
+          <t>78822</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>175221</t>
+          <t>174449</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>222941</t>
+          <t>225885</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,83%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>367346</t>
+          <t>366873</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>406986</t>
+          <t>405194</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>88480</t>
+          <t>87301</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>113760</t>
+          <t>113390</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>465095</t>
+          <t>462151</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>512815</t>
+          <t>513587</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,65%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>257354</t>
+          <t>257748</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>315215</t>
+          <t>316218</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>199981</t>
+          <t>201222</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>252463</t>
+          <t>254007</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>473436</t>
+          <t>472704</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>550712</t>
+          <t>551341</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>834423</t>
+          <t>833420</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>892284</t>
+          <t>891890</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>573413</t>
+          <t>571869</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>625895</t>
+          <t>624654</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1424802</t>
+          <t>1424173</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1502078</t>
+          <t>1502810</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,07%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>136943</t>
+          <t>137785</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>180811</t>
+          <t>179465</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>276583</t>
+          <t>279317</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>331380</t>
+          <t>332671</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>426008</t>
+          <t>427630</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>497697</t>
+          <t>495954</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,5%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>439895</t>
+          <t>441241</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>483763</t>
+          <t>482921</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>406864</t>
+          <t>405573</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>461661</t>
+          <t>458927</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>861253</t>
+          <t>862996</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>932942</t>
+          <t>931320</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,53%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>11396</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29247</t>
+          <t>28956</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>431748</t>
+          <t>433774</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>499907</t>
+          <t>503281</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>446299</t>
+          <t>450936</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>521418</t>
+          <t>524790</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,33%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>257898</t>
+          <t>258189</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>274685</t>
+          <t>275749</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>582118</t>
+          <t>578744</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>650277</t>
+          <t>648251</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>847752</t>
+          <t>844380</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>922871</t>
+          <t>918234</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>67,07%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>730826</t>
+          <t>731167</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>831196</t>
+          <t>828832</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1166568</t>
+          <t>1173916</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1282080</t>
+          <t>1289227</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1923225</t>
+          <t>1927768</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2084150</t>
+          <t>2078101</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,04%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2554526</t>
+          <t>2556890</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2654896</t>
+          <t>2654555</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2249516</t>
+          <t>2242369</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2365028</t>
+          <t>2357680</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4833168</t>
+          <t>4839217</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4994093</t>
+          <t>4989550</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,13%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>122034</t>
+          <t>121639</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>162110</t>
+          <t>163134</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>124915</t>
+          <t>124548</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>157323</t>
+          <t>157462</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>256365</t>
+          <t>256539</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>308146</t>
+          <t>306718</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,2%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>343102</t>
+          <t>342078</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>383178</t>
+          <t>383573</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>290144</t>
+          <t>290005</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>322552</t>
+          <t>322919</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>644533</t>
+          <t>645961</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>696314</t>
+          <t>696140</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,07%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>105239</t>
+          <t>104895</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>143495</t>
+          <t>139841</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>109462</t>
+          <t>110755</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>140183</t>
+          <t>141000</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>225709</t>
+          <t>227148</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>272053</t>
+          <t>271862</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,57%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>308718</t>
+          <t>312372</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>346974</t>
+          <t>347318</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>242397</t>
+          <t>241580</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>273118</t>
+          <t>271825</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>562740</t>
+          <t>562931</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>609084</t>
+          <t>607645</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>72,79%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50068</t>
+          <t>54696</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>232106</t>
+          <t>232750</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>77371</t>
+          <t>77086</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>98305</t>
+          <t>97755</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98391</t>
+          <t>108990</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>331964</t>
+          <t>329202</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,42%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>436158</t>
+          <t>435514</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>618196</t>
+          <t>613568</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68606</t>
+          <t>69156</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89540</t>
+          <t>89825</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>503211</t>
+          <t>505973</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>736784</t>
+          <t>726185</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>86,95%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>327500</t>
+          <t>327446</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>396113</t>
+          <t>394461</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>366877</t>
+          <t>365110</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>729400</t>
+          <t>693345</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>713541</t>
+          <t>717632</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1174603</t>
+          <t>1228102</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>61,01%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>638706</t>
+          <t>640358</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>707319</t>
+          <t>707373</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>248694</t>
+          <t>284749</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>611217</t>
+          <t>612984</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>838309</t>
+          <t>784810</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1299371</t>
+          <t>1295280</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,35%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>136378</t>
+          <t>136196</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>178737</t>
+          <t>179294</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>264407</t>
+          <t>273947</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>417114</t>
+          <t>419806</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>429518</t>
+          <t>425966</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>572822</t>
+          <t>570399</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,33%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>296309</t>
+          <t>295752</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>338668</t>
+          <t>338850</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>424221</t>
+          <t>421529</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>576928</t>
+          <t>567388</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>743559</t>
+          <t>745982</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>886863</t>
+          <t>890415</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,64%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11706</t>
+          <t>13033</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40667</t>
+          <t>40039</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>305946</t>
+          <t>306542</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>356517</t>
+          <t>357213</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>321342</t>
+          <t>324488</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>382234</t>
+          <t>388852</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,81%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>199840</t>
+          <t>200468</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>228801</t>
+          <t>227474</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>404854</t>
+          <t>404158</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>455425</t>
+          <t>454829</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>619644</t>
+          <t>613026</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>680536</t>
+          <t>677390</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,61%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>713594</t>
+          <t>745908</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1036034</t>
+          <t>1030521</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1403568</t>
+          <t>1404528</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1939646</t>
+          <t>1918810</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2233513</t>
+          <t>2271523</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2878464</t>
+          <t>2950347</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>42,43%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2340026</t>
+          <t>2345539</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2662466</t>
+          <t>2630152</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1638112</t>
+          <t>1658948</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2174190</t>
+          <t>2173230</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4075354</t>
+          <t>4003471</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4720305</t>
+          <t>4682295</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>67,33%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A_n_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R2-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>64594</t>
+          <t>63932</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97754</t>
+          <t>98159</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54253</t>
+          <t>56951</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>85608</t>
+          <t>85004</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>127602</t>
+          <t>127944</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>170517</t>
+          <t>172130</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>376022</t>
+          <t>375617</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>409182</t>
+          <t>409844</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>221072</t>
+          <t>221676</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>252427</t>
+          <t>249729</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>609940</t>
+          <t>608327</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>652855</t>
+          <t>652513</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,61%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39366</t>
+          <t>37743</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67027</t>
+          <t>66058</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70835</t>
+          <t>71070</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>103732</t>
+          <t>102659</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116855</t>
+          <t>116624</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>159758</t>
+          <t>158839</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,5%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>299907</t>
+          <t>300876</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>327568</t>
+          <t>329191</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>268133</t>
+          <t>269206</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>301030</t>
+          <t>300795</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>579041</t>
+          <t>579960</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>621944</t>
+          <t>622175</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,21%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77033</t>
+          <t>78225</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>111417</t>
+          <t>111916</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35128</t>
+          <t>34759</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58086</t>
+          <t>57540</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>119456</t>
+          <t>119303</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>162950</t>
+          <t>159897</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>430972</t>
+          <t>430473</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>465356</t>
+          <t>464164</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>109696</t>
+          <t>110242</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>132654</t>
+          <t>133023</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>547221</t>
+          <t>550274</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>590715</t>
+          <t>590868</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,2%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>241643</t>
+          <t>241057</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>301820</t>
+          <t>298010</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>162956</t>
+          <t>165461</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>210140</t>
+          <t>210385</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>417959</t>
+          <t>418965</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>491417</t>
+          <t>489661</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,08%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>936514</t>
+          <t>940324</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>996691</t>
+          <t>997277</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>504145</t>
+          <t>503900</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>551329</t>
+          <t>548824</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1461203</t>
+          <t>1462959</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1534661</t>
+          <t>1533655</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,54%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48777</t>
+          <t>48581</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>76099</t>
+          <t>77182</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>141897</t>
+          <t>144915</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>187055</t>
+          <t>188470</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>199991</t>
+          <t>200611</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>254203</t>
+          <t>253651</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,59%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>274456</t>
+          <t>273373</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>301778</t>
+          <t>301974</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>381697</t>
+          <t>380282</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>426855</t>
+          <t>423837</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>665104</t>
+          <t>665656</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>719316</t>
+          <t>718696</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,18%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>9603</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26010</t>
+          <t>25695</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>418682</t>
+          <t>422347</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>486354</t>
+          <t>487802</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>435135</t>
+          <t>431807</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>509440</t>
+          <t>506492</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,74%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>272191</t>
+          <t>272506</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287986</t>
+          <t>288598</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>762406</t>
+          <t>760958</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>830078</t>
+          <t>826413</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1037520</t>
+          <t>1040468</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1111825</t>
+          <t>1115153</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>72,09%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>531241</t>
+          <t>529316</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>616328</t>
+          <t>611582</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>956852</t>
+          <t>953366</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1060443</t>
+          <t>1060286</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1499621</t>
+          <t>1505573</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1641852</t>
+          <t>1649696</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,81%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2653862</t>
+          <t>2658608</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2738949</t>
+          <t>2740874</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2317681</t>
+          <t>2317838</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2421272</t>
+          <t>2424758</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5006462</t>
+          <t>4998618</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5148693</t>
+          <t>5142741</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,35%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74550</t>
+          <t>75642</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>112871</t>
+          <t>111111</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61600</t>
+          <t>63012</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>95650</t>
+          <t>94331</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>146848</t>
+          <t>146958</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>193388</t>
+          <t>194684</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,9%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>324340</t>
+          <t>326100</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>362661</t>
+          <t>361569</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>218804</t>
+          <t>220123</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>252854</t>
+          <t>251442</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>558277</t>
+          <t>556981</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>604817</t>
+          <t>604707</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,45%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71110</t>
+          <t>71143</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>106007</t>
+          <t>108150</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>78309</t>
+          <t>79558</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>113982</t>
+          <t>113873</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>159357</t>
+          <t>159379</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>209058</t>
+          <t>211102</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,89%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>312790</t>
+          <t>310647</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>347687</t>
+          <t>347654</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>224029</t>
+          <t>224138</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>259702</t>
+          <t>258453</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>547750</t>
+          <t>545706</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>597451</t>
+          <t>597429</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>170545</t>
+          <t>171418</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>218878</t>
+          <t>218778</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>83115</t>
+          <t>82325</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>114046</t>
+          <t>114516</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>261280</t>
+          <t>262970</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>320675</t>
+          <t>319357</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,9%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>410537</t>
+          <t>410637</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>458870</t>
+          <t>457997</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>146083</t>
+          <t>145613</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>177014</t>
+          <t>177804</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>568869</t>
+          <t>570187</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>628264</t>
+          <t>626574</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,44%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>303482</t>
+          <t>301773</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>368051</t>
+          <t>367456</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>227621</t>
+          <t>231025</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>282765</t>
+          <t>287857</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>550572</t>
+          <t>549601</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>637495</t>
+          <t>635320</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>32,99%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>790958</t>
+          <t>791553</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>855527</t>
+          <t>857236</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>483892</t>
+          <t>478800</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>539036</t>
+          <t>535632</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1288172</t>
+          <t>1290347</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1375095</t>
+          <t>1376066</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,46%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>114716</t>
+          <t>112388</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>153916</t>
+          <t>153537</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>330090</t>
+          <t>326919</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>385372</t>
+          <t>384859</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>452171</t>
+          <t>454088</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>523690</t>
+          <t>521364</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>40,98%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>357059</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>395880</t>
+          <t>398208</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>376150</t>
+          <t>376663</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>431432</t>
+          <t>434603</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>748428</t>
+          <t>750754</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>819947</t>
+          <t>818030</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,3%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13179</t>
+          <t>13207</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32761</t>
+          <t>32323</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>504572</t>
+          <t>500598</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>569457</t>
+          <t>570907</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>519858</t>
+          <t>517043</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>596259</t>
+          <t>591270</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>42,96%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>234121</t>
+          <t>234559</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>253703</t>
+          <t>253675</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>539894</t>
+          <t>538444</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>604779</t>
+          <t>608753</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>779974</t>
+          <t>784963</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>856375</t>
+          <t>859190</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,43%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>815915</t>
+          <t>812973</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>922354</t>
+          <t>919965</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1361852</t>
+          <t>1356258</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1481394</t>
+          <t>1479517</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2204525</t>
+          <t>2210707</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2361372</t>
+          <t>2366671</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,95%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2499556</t>
+          <t>2501945</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2605995</t>
+          <t>2608937</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2068731</t>
+          <t>2070608</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2188273</t>
+          <t>2193867</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4610663</t>
+          <t>4605364</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4767510</t>
+          <t>4761328</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,29%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>77313</t>
+          <t>76928</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114515</t>
+          <t>112912</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61664</t>
+          <t>61053</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>93075</t>
+          <t>92513</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>146917</t>
+          <t>149348</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>195397</t>
+          <t>195788</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,23%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>314577</t>
+          <t>316180</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>351779</t>
+          <t>352164</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>253980</t>
+          <t>254542</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285391</t>
+          <t>286002</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>580750</t>
+          <t>580359</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>629230</t>
+          <t>626799</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>80,76%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67929</t>
+          <t>69244</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>101952</t>
+          <t>102821</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74904</t>
+          <t>74362</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108301</t>
+          <t>109532</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>153795</t>
+          <t>152381</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>200305</t>
+          <t>199583</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,63%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>275275</t>
+          <t>274406</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>309298</t>
+          <t>307983</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>263972</t>
+          <t>262741</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>297369</t>
+          <t>297911</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>549195</t>
+          <t>549917</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>595705</t>
+          <t>597119</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,67%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>116720</t>
+          <t>115634</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155041</t>
+          <t>154343</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52733</t>
+          <t>51714</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78822</t>
+          <t>79037</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>174449</t>
+          <t>175906</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>225885</t>
+          <t>223561</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>366873</t>
+          <t>367571</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>405194</t>
+          <t>406280</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>87301</t>
+          <t>87086</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>113390</t>
+          <t>114409</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>462151</t>
+          <t>464475</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>513587</t>
+          <t>512130</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,43%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>257748</t>
+          <t>257148</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>316218</t>
+          <t>315306</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>201222</t>
+          <t>199462</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>254007</t>
+          <t>250385</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>472704</t>
+          <t>470540</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>551341</t>
+          <t>549583</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,82%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>833420</t>
+          <t>834332</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>891890</t>
+          <t>892490</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>571869</t>
+          <t>575491</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>624654</t>
+          <t>626414</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1424173</t>
+          <t>1425931</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1502810</t>
+          <t>1504974</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,18%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>137785</t>
+          <t>139173</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>179465</t>
+          <t>182068</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>279317</t>
+          <t>276662</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>332671</t>
+          <t>333178</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>427630</t>
+          <t>427779</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>495954</t>
+          <t>495108</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,43%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>441241</t>
+          <t>438638</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>482921</t>
+          <t>481533</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>405573</t>
+          <t>405066</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>458927</t>
+          <t>461582</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>862996</t>
+          <t>863842</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>931320</t>
+          <t>931171</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,52%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11396</t>
+          <t>11809</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28956</t>
+          <t>29826</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>433774</t>
+          <t>433941</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>503281</t>
+          <t>501184</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>450936</t>
+          <t>453259</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>524790</t>
+          <t>528610</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,61%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258189</t>
+          <t>257319</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>275749</t>
+          <t>275336</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>578744</t>
+          <t>580841</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>648251</t>
+          <t>648084</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>844380</t>
+          <t>840560</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>918234</t>
+          <t>915911</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>66,9%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>731167</t>
+          <t>724506</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>828832</t>
+          <t>829541</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1173916</t>
+          <t>1167923</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1289227</t>
+          <t>1285810</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1927768</t>
+          <t>1926296</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2078101</t>
+          <t>2079915</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,07%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2556890</t>
+          <t>2556181</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2654555</t>
+          <t>2661216</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2242369</t>
+          <t>2245786</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2357680</t>
+          <t>2363673</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4839217</t>
+          <t>4837403</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4989550</t>
+          <t>4991022</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,15%</t>
         </is>
       </c>
     </row>
@@ -8633,102 +8633,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>140993</t>
+          <t>153134</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>121639</t>
+          <t>132188</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>163134</t>
+          <t>173082</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>31,43%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>151492</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>134968</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>169593</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>31,02%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>27,63%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>34,72%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>304626</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>279624</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>335498</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>29,32%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>26,91%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>32,29%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>140519</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>124548</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>157462</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>31,4%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>27,83%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>35,19%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>413</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>281512</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>256539</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>306718</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>29,55%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>26,93%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>32,2%</t>
         </is>
       </c>
     </row>
@@ -8746,102 +8746,102 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>364219</t>
+          <t>397484</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>342078</t>
+          <t>377536</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>383573</t>
+          <t>418430</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>68,57%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>75,99%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>336919</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>318818</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>353443</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>68,98%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>65,28%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>72,37%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>827</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>734403</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>703531</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>759405</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>70,68%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>67,71%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>75,92%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>452</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>306948</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>290005</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>322919</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>68,6%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>64,81%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>72,17%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>827</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>671167</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>645961</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>696140</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>70,45%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>67,8%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>73,09%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>122317</t>
+          <t>130760</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>104895</t>
+          <t>112162</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>139841</t>
+          <t>149958</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>125734</t>
+          <t>136776</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>110755</t>
+          <t>121217</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>141000</t>
+          <t>153835</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>248051</t>
+          <t>267536</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>227148</t>
+          <t>244365</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>271862</t>
+          <t>292695</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,29%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>329896</t>
+          <t>352452</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>312372</t>
+          <t>333254</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>347318</t>
+          <t>371050</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>256846</t>
+          <t>286367</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>241580</t>
+          <t>269308</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>271825</t>
+          <t>301926</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>586742</t>
+          <t>638819</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>562931</t>
+          <t>613660</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>607645</t>
+          <t>661990</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>73,04%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>141667</t>
+          <t>151486</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54696</t>
+          <t>133834</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>232750</t>
+          <t>173043</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>87089</t>
+          <t>96274</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>77086</t>
+          <t>85131</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>97755</t>
+          <t>108348</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>228756</t>
+          <t>247760</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>108990</t>
+          <t>224279</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>329202</t>
+          <t>271600</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>41,21%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>526597</t>
+          <t>320126</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>435514</t>
+          <t>298569</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>613568</t>
+          <t>337778</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>79822</t>
+          <t>91223</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69156</t>
+          <t>79149</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89825</t>
+          <t>102366</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>606419</t>
+          <t>411349</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>505973</t>
+          <t>387509</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>726185</t>
+          <t>434830</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>65,97%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>358351</t>
+          <t>390771</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>327446</t>
+          <t>356047</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>394461</t>
+          <t>423927</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>502045</t>
+          <t>328892</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>365110</t>
+          <t>306677</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>693345</t>
+          <t>355343</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>860395</t>
+          <t>719663</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>717632</t>
+          <t>679059</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1228102</t>
+          <t>759505</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>38,11%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>676468</t>
+          <t>741072</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>640358</t>
+          <t>707916</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>707373</t>
+          <t>775796</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>476049</t>
+          <t>532319</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>284749</t>
+          <t>505868</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>612984</t>
+          <t>554534</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1152517</t>
+          <t>1273391</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>784810</t>
+          <t>1233549</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1295280</t>
+          <t>1313995</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>65,93%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>156828</t>
+          <t>176260</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>136196</t>
+          <t>154750</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>179294</t>
+          <t>199410</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>366475</t>
+          <t>399519</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>273947</t>
+          <t>375739</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>419806</t>
+          <t>424430</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>523303</t>
+          <t>575780</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>425966</t>
+          <t>545118</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>570399</t>
+          <t>610423</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>43,64%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>318218</t>
+          <t>391704</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>295752</t>
+          <t>368554</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>338850</t>
+          <t>413214</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>474860</t>
+          <t>431331</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>421529</t>
+          <t>406420</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>567388</t>
+          <t>455111</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>793078</t>
+          <t>823034</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>745982</t>
+          <t>788391</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>890415</t>
+          <t>853696</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>61,03%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23099</t>
+          <t>24472</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13033</t>
+          <t>13489</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40039</t>
+          <t>42098</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>331619</t>
+          <t>358347</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>306542</t>
+          <t>333404</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>357213</t>
+          <t>385824</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>354718</t>
+          <t>382820</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>324488</t>
+          <t>350381</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>388852</t>
+          <t>411882</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,08%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>217408</t>
+          <t>212756</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>200468</t>
+          <t>195130</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>227474</t>
+          <t>223739</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>429752</t>
+          <t>485934</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>404158</t>
+          <t>458457</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>454829</t>
+          <t>510877</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>647160</t>
+          <t>698689</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>613026</t>
+          <t>669627</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>677390</t>
+          <t>731128</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,6%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>943254</t>
+          <t>1026884</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>745908</t>
+          <t>966937</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1030521</t>
+          <t>1086289</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1553481</t>
+          <t>1471300</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1404528</t>
+          <t>1423024</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1918810</t>
+          <t>1523111</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2496735</t>
+          <t>2498184</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2271523</t>
+          <t>2420718</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2950347</t>
+          <t>2572646</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>36,35%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2432806</t>
+          <t>2415592</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2345539</t>
+          <t>2356187</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2630152</t>
+          <t>2475539</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2024277</t>
+          <t>2164093</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1658948</t>
+          <t>2112282</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2173230</t>
+          <t>2212369</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>4457083</t>
+          <t>4579685</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4003471</t>
+          <t>4505223</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4682295</t>
+          <t>4657151</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>65,8%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
